--- a/dakimakury.xlsx
+++ b/dakimakury.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I2"/>
+  <dimension ref="A1:I128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,38 +471,5960 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>170x50 см</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Велюр</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Холлофайбер</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>533</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2800</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>images\sakura_colored.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Лунная фея</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Персиковая кожа</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Пена с памятью</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Светится в темноте, Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>3200</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>images\moon_fairy.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Снежная королева</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>160x60 см</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Полиэстер</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Велюр</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
         <is>
           <t>Холлофайбер</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Двусторонняя печать, HD Качество</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Односторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
         <is>
           <t>Гипоаллергенная</t>
         </is>
       </c>
-      <c r="G2" t="n">
-        <v>13</v>
-      </c>
-      <c r="H2" t="n">
-        <v>2796</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>images\sakura_colored.png</t>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2700</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>images\snow_queen.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Катана-воительница</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Шёлк</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Синтепон</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, 4K печать</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Антибактериальная пропитка</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>images\katana_warrior.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Демон севера</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Микрофибра</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Холлофайбер</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Термостойкая</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2900</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>images\demon_north.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Весенний ветер</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Велюр</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Пух</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Односторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Мягкая поверхность</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2600</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>images\spring_wind.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Морская принцесса</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Персиковая кожа</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Холлофайбер</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Водоотталкивающая, Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>3100</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>images\sea_princess.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Огненная лисица</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Шёлк</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Пена с памятью</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, 4K печать</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Антибактериальная пропитка, Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>3800</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>images\fire_fox.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Звёздный ангел</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Велюр</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Синтепон</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Односторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>images\star_angel.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Дракон рассвета</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Микрофибра</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Холлофайбер</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Термостойкая</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>images\dawn_dragon.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Чайная церемония</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Бамбуковое волокно</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Холлофайбер</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Эко-материал, Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>3300</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>images\tea_ceremony.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Небесный лотос</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Персиковая кожа</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Синтепон</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, 4K печать</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Мягкая поверхность, Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>3600</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>images\sky_lotus.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Ночная охотница</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Шёлк</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Пена с памятью</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Антибактериальная пропитка</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>3400</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>images\night_hunter.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Розовый самурай</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Велюр</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Холлофайбер</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Односторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2800</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>images\pink_samurai.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Лесная нимфа</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Микрофибра</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Пух</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Эко-материал</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2950</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>images\forest_nymph.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Кицунэ-хранитель</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Бамбуковое волокно</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Холлофайбер</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, 4K печать</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Эко-материал</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>3700</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>images\kitsune.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Звук грома</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Персиковая кожа</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Синтепон</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Антибактериальная пропитка</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>3050</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>images\thunder.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Рубиновая мечта</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Шёлк</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Пена с памятью</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, 4K печать</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Мягкая поверхность</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>images\ruby_dream.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Цветок магнолии</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Велюр</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Холлофайбер</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Односторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>280</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2700</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>images\magnolia.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Северное сияние</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Микрофибра</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Холлофайбер</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Светится в темноте</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>3250</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>images\aurora.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Хранительница храма</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Бамбуковое волокно</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Пух</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Эко-материал, Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>3100</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>images\temple_guardian.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Пурпурный закат</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Персиковая кожа</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Пена с памятью</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, 4K печать</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Антибактериальная пропитка, Термостойкая</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>3900</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>images\purple_sunset.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Ледяная волшебница</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Шёлк</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Синтепон</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>3450</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>images\ice_witch.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Золотой феникс</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Велюр</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Холлофайбер</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, 4K печать</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Мягкая поверхность</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>3600</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>images\golden_phoenix.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Морской бриз</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Микрофибра</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Пух</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Односторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Водоотталкивающая, Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2600</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>images\sea_breeze.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Тихая гейша</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Бамбуковое волокно</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Меморифоам</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Эко-материал</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>3150</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>images\quiet_geisha.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Алая стрела</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Персиковая кожа</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Пена с памятью</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Антибактериальная пропитка</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>3550</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>images\crimson_arrow.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Облачный дракон</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Шёлк</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Синтепон</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, 4K печать</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>3800</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>images\cloud_dragon.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Лунный кролик</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Велюр</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Меморифоам</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Односторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Мягкая поверхность, Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>images\moon_rabbit.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Таинственный лес</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Микрофибра</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Пена с памятью</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Светится в темноте, Эко-материал</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>3300</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>images\mystic_forest.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Цветочный шторм</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Бамбуковое волокно</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Меморифоам</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Эко-материал, Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2900</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>images\flower_storm.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Стальная валькирия</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Персиковая кожа</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Синтепон</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, 4K печать</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Антибактериальная пропитка, Термостойкая</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>4100</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>images\steel_valkyrie.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Нежный рассвет</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Шёлк</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Пух</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Мягкая поверхность</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>3200</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>images\gentle_dawn.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Вишнёвый ветер</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Велюр</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Меморифоам</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Односторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>410</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>images\cherry_wind.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Звёздная кошка</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Микрофибра</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Пена с памятью</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Антибактериальная пропитка</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>3050</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>images\star_cat.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Горный поток</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Бамбуковое волокно</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Синтепон</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, 4K печать</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Эко-материал, Водоотталкивающая</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>3650</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>images\mountain_stream.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Фиолетовая ведьма</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Персиковая кожа</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Холлофайбер</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Светится в темноте</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>3350</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>images\violet_witch.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Цветущая слива</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Шёлк</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Пух</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, 4K печать</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>3900</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>images\plum_blossom.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Летний дождь</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Велюр</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Холлофайбер</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Односторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Водоотталкивающая</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2650</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>images\summer_rain.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Призрак луны</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Микрофибра</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Пена с памятью</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Светится в темноте, Антибактериальная пропитка</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>3400</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>images\moon_ghost.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Багровый дракон</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Бамбуковое волокно</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Меморифоам</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, 4K печать</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Эко-материал, Термостойкая</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>3750</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>images\crimson_dragon.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Белый лебедь</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Персиковая кожа</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Холлофайбер</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Мягкая поверхность</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>3100</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>images\white_swan.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Электрический ниндзя</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Шёлк</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Пена с памятью</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, 4K печать</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Антибактериальная пропитка</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>4200</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>images\electric_ninja.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Ромашковый луг</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Велюр</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Пух</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Односторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Эко-материал</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2450</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>images\daisy_field.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Тёмный маг</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Микрофибра</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Холлофайбер</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Светится в темноте</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>3200</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>images\dark_mage.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Персиковая богиня</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Бамбуковое волокно</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Синтепон</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, 4K печать</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Эко-материал, Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>3850</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>images\peach_goddess.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Серебряная волчица</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Персиковая кожа</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Пена с памятью</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Антибактериальная пропитка</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>3300</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>images\silver_wolf.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Японский сад</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Шёлк</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Меморифоам</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>3550</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>images\japanese_garden.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Весенняя нимфа</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Велюр</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Пух</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Односторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Мягкая поверхность, Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2700</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>images\spring_nymph.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Полярная лиса</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Микрофибра</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Пена с памятью</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, 4K печать</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Термостойкая</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>3700</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>images\polar_fox.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Волна океана</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Бамбуковое волокно</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Синтепон</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Эко-материал, Водоотталкивающая</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2950</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>images\ocean_wave.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Призрак цветка</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Персиковая кожа</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Холлофайбер</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>3150</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>images\flower_ghost.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Небесный воин</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Шёлк</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Пена с памятью</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, 4K печать</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Антибактериальная пропитка, Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>4300</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>images\sky_warrior.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Коралловый закат</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Велюр</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Пух</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Мягкая поверхность</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2600</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>images\coral_sunset.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Радужная фея</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Микрофибра</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Холлофайбер</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Односторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Светится в темноте</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>images\rainbow_fairy.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Таинственная маска</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Бамбуковое волокно</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Синтепон</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, 4K печать</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Эко-материал, Антибактериальная пропитка</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>3950</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>images\mystery_mask.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Кленовый лист</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Персиковая кожа</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Пена с памятью</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>3250</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>images\maple_leaf.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Тёмная принцесса</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Шёлк</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Холлофайбер</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Термостойкая</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>3600</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>images\dark_princess.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Весенний поток</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Велюр</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Пух</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Односторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Водоотталкивающая</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>395</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>images\spring_stream.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Золотая змея</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Микрофибра</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Пена с памятью</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, 4K печать</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Антибактериальная пропитка</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>3800</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>images\golden_snake.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Хризантема</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Бамбуковое волокно</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Синтепон</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Эко-материал, Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>2850</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>images\chrysanthemum.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Ночной мотылёк</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Персиковая кожа</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Холлофайбер</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Светится в темноте, Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>3450</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>images\night_moth.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Белый тигр</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Шёлк</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>Пена с памятью</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, 4K печать</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Антибактериальная пропитка, Термостойкая</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>images\white_tiger.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Акварельный сон</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Велюр</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Пух</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Мягкая поверхность</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>2750</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>images\watercolor_dream.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Лазурный горизонт</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Микрофибра</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Холлофайбер</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Односторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2900</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>images\azure_horizon.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Красный кардинал</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Бамбуковое волокно</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Синтепон</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, 4K печать</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Эко-материал, Антибактериальная пропитка</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>images\red_cardinal.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Магический зеркала</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Персиковая кожа</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Пена с памятью</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Светится в темноте</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>images\magic_mirror.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Тихий пруд</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Шёлк</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Холлофайбер</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>3300</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>images\quiet_pond.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Розовый дракончик</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Велюр</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Пух</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, 4K печать</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Мягкая поверхность, Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>2800</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>images\pink_dragon.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Демон цветов</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Микрофибра</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Пена с памятью</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Антибактериальная пропитка, Термостойкая</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>3700</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>images\flower_demon.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Небесный олень</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Бамбуковое волокно</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Синтепон</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Эко-материал, Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>2950</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>images\sky_deer.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Хрустальный водопад</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Персиковая кожа</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Холлофайбер</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, 4K печать</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Водоотталкивающая</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>3850</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>images\crystal_waterfall.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Осенний лист</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Шёлк</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Пена с памятью</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Мягкая поверхность</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>3600</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>images\autumn_leaf.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Зимняя фея</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Велюр</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Пух</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Односторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2550</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>images\winter_fairy.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Турмалиновый кот</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Микрофибра</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Холлофайбер</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Антибактериальная пропитка, Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>3050</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>images\tourmaline_cat.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Сапфировый ветер</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Бамбуковое волокно</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Синтепон</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, 4K печать</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Эко-материал, Термостойкая</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>4050</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>images\sapphire_wind.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Закат на озере</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Персиковая кожа</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Пена с памятью</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Светится в темноте</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>3150</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>images\lake_sunset.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Магнолиевый сад</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Шёлк</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Холлофайбер</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>3400</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>images\magnolia_garden.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Лиловая звезда</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Велюр</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Пух</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Односторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Мягкая поверхность, Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>2700</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>images\lilac_star.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Тёмный рыцарь</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Микрофибра</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Пена с памятью</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, 4K печать</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Антибактериальная пропитка, Термостойкая</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>3950</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>images\dark_knight.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Цветок ириса</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Бамбуковое волокно</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Синтепон</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Эко-материал, Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>2900</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>images\iris_flower.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Пламенная птица</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Персиковая кожа</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Холлофайбер</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Светится в темноте</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>3250</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>images\flame_bird.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Изумрудный лес</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Шёлк</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Пена с памятью</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, 4K печать</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Антибактериальная пропитка, Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>4400</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>images\emerald_forest.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Облачная дева</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Велюр</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Пух</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Мягкая поверхность</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>2600</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>images\cloud_maiden.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Стальной орёл</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Микрофибра</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Холлофайбер</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Термостойкая, Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>images\steel_eagle.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Бирюзовый дракон</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Бамбуковое волокно</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Синтепон</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, 4K печать</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Эко-материал, Антибактериальная пропитка</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>3750</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>images\turquoise_dragon.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Розовый закат</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Персиковая кожа</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Пена с памятью</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Водоотталкивающая</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>3100</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>images\pink_sunset.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Лесная волшебница</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Шёлк</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Холлофайбер</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>3500</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>images\forest_witch.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Янтарный закат</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Велюр</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Пух</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Односторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Мягкая поверхность, Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>2650</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>images\amber_sunset.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Серебряный кролик</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Микрофибра</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Пена с памятью</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, 4K печать</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Антибактериальная пропитка</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>3800</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>images\silver_rabbit.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Сакуральный дождь</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Бамбуковое волокно</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Синтепон</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Эко-материал, Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>2850</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>images\sakura_rain.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Золотой лотос</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Персиковая кожа</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Холлофайбер</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Светится в темноте</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>3350</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>images\golden_lotus.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Снежный барс</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Шёлк</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Пена с памятью</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, 4K печать</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Антибактериальная пропитка, Термостойкая</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>4250</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>images\snow_leopard.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Вечерняя звезда</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Велюр</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Пух</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Мягкая поверхность</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>2500</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>images\evening_star.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Морской дракон</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Микрофибра</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Холлофайбер</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Водоотталкивающая, Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>3050</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>images\sea_dragon.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Нефритовая богиня</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Бамбуковое волокно</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Синтепон</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, 4K печать</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Эко-материал, Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>3900</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>images\jade_goddess.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Алмазный ветер</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Персиковая кожа</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Пена с памятью</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Антибактериальная пропитка</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>3200</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>images\diamond_wind.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Полночная ведьма</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Шёлк</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Холлофайбер</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Светится в темноте</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>3650</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>images\midnight_witch.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Нежная роза</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Велюр</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Пух</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Односторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>2700</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>images\tender_rose.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Ледяной феникс</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Микрофибра</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Пена с памятью</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, 4K печать</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Антибактериальная пропитка, Термостойкая</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>4150</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>images\ice_phoenix.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Пионовый сад</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Бамбуковое волокно</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Синтепон</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Эко-материал, Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>2900</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>images\peony_garden.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Звёздная воительница</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Персиковая кожа</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Холлофайбер</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>3400</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>images\star_warrior.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Тёмный дракон</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Шёлк</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Пена с памятью</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, 4K печать</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Антибактериальная пропитка, Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>4600</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>images\dark_dragon.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Лавандовый рассвет</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Велюр</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Пух</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Мягкая поверхность, Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2600</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>images\lavender_dawn.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Огненный дух</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Микрофибра</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Холлофайбер</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Термостойкая</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>3100</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>images\fire_spirit.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Хрустальная фея</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Бамбуковое волокно</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Синтепон</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, 4K печать</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Эко-материал, Антибактериальная пропитка</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>3950</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>images\crystal_fairy.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Ночной страж</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Персиковая кожа</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Пена с памятью</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Светится в темноте</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>3300</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>images\night_guard.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Персиковый цветок</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Шёлк</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Холлофайбер</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>3550</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>images\peach_flower.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Синяя птица</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Велюр</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Пух</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Односторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Мягкая поверхность, Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>278</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>2650</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>images\blue_bird.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Лунный воин</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Микрофибра</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Пена с памятью</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, 4K печать</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Антибактериальная пропитка, Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>4050</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>images\moon_warrior.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Гранатовый цветок</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Бамбуковое волокно</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Синтепон</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Эко-материал, Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>2950</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>images\pomegranate_flower.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Белая магия</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Персиковая кожа</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Холлофайбер</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Антибактериальная пропитка</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>3200</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>images\white_magic.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Алый феникс</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Шёлк</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Пена с памятью</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, 4K печать</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Антибактериальная пропитка, Термостойкая</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>4400</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>images\scarlet_phoenix.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Мечтательный лес</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Велюр</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Пух</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Мягкая поверхность</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>2550</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>images\dreamy_forest.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Бриллиантовая принцесса</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Микрофибра</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Холлофайбер</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Светится в темноте</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>3050</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>images\diamond_princess.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Изумрудная змея</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Бамбуковое волокно</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Синтепон</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, 4K печать</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Эко-материал, Антибактериальная пропитка</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>3800</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>images\emerald_snake.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Дорога к звёздам</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Персиковая кожа</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Пена с памятью</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>3150</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>images\road_to_stars.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Лотосовый пруд</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Шёлк</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Холлофайбер</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Водоотталкивающая</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>3450</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>images\lotus_pond.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Розовый рассвет</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Велюр</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Пух</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Односторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Мягкая поверхность, Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>2700</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>images\pink_dawn.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Штормовой воин</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Микрофибра</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Пена с памятью</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, 4K печать</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Антибактериальная пропитка, Термостойкая</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>4100</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>images\storm_warrior.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Нежный пион</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Бамбуковое волокно</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Синтепон</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Эко-материал, Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>2900</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>images\tender_peony.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Кристальный лёд</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Персиковая кожа</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Холлофайбер</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Светится в темноте</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>3350</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>images\crystal_ice.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Тёмный омут</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Шёлк</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Пена с памятью</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, 4K печать</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Антибактериальная пропитка, Гипоаллергенная</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>4700</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>images\dark_pool.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Солнечный зайчик</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Велюр</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Пух</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Мягкая поверхность</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>420</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>2450</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>images\sun_bunny.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Пурпурный феникс</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Микрофибра</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Холлофайбер</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Термостойкая</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>images\purple_phoenix.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Изумрудный дракон</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>150x50 см</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Бамбуковое волокно</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Синтепон</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, 4K печать</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Эко-материал, Антибактериальная пропитка</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>3850</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>images\emerald_dragon.png</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Лунная принцесса</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>160x60 см</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Персиковая кожа</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Пена с памятью</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Двусторонняя печать, HD Качество</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Гипоаллергенная, Светится в темноте</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>3200</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>images\moon_princess.png</t>
         </is>
       </c>
     </row>
